--- a/data/trans_dic/IP12B$cabeza-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,8</t>
+          <t>0,0; 35,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,58</t>
+          <t>0,0; 21,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,01</t>
+          <t>0,0; 47,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,8</t>
+          <t>0,0; 39,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,84</t>
+          <t>0,0; 16,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,53</t>
+          <t>0,0; 16,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,17</t>
+          <t>0,0; 32,84</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 22,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,49</t>
+          <t>0,0; 14,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,1</t>
+          <t>0,0; 20,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,45</t>
+          <t>0,0; 28,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,03</t>
+          <t>0,0; 9,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,91</t>
+          <t>0,0; 15,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,05</t>
+          <t>0,0; 14,69</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,75</t>
+          <t>0,0; 24,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,3</t>
+          <t>0,0; 31,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,18</t>
+          <t>0,0; 32,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,89</t>
+          <t>0,0; 26,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,13</t>
+          <t>0,0; 19,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,31</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,04</t>
+          <t>0,0; 15,74</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,0</t>
+          <t>0,0; 44,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,68</t>
+          <t>0,0; 25,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,46</t>
+          <t>0,0; 33,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,44</t>
+          <t>0,0; 23,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,79</t>
+          <t>0,0; 20,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 16,6</t>
+          <t>1,86; 17,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,7</t>
+          <t>0,0; 13,26</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,69</t>
+          <t>1,44; 13,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,7</t>
+          <t>2,16; 12,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 12,26</t>
+          <t>1,17; 13,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,39</t>
+          <t>1,1; 11,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,04</t>
+          <t>0,0; 12,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,32</t>
+          <t>1,42; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 9,07</t>
+          <t>2,21; 9,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,06</t>
+          <t>1,37; 8,93</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1133</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4348</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3634</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4255</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4043</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4011</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4614</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5251</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1544</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4222</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2939</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3380</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4410</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2751</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5039</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5263</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3127</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2664</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4250</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4138</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2691</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4334</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1633</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3035</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4022</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4823</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4964</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3532</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>681; 6546</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3133</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2158</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2531</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3475</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>631; 5838</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1321; 7408</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>645; 7630</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4515</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>699; 7449</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6036</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1283; 7126</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2760; 11640</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1413; 9195</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$cabeza-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,52</t>
+          <t>0,0; 26,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,2</t>
+          <t>0,0; 16,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,96</t>
+          <t>0,0; 52,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,59</t>
+          <t>0,0; 33,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,69</t>
+          <t>0,0; 16,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,87</t>
+          <t>0,0; 17,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,84</t>
+          <t>0,0; 33,97</t>
         </is>
       </c>
     </row>
@@ -793,17 +793,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,01</t>
+          <t>0,0; 22,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,5</t>
+          <t>0,0; 15,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,94</t>
+          <t>0,0; 20,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,35</t>
+          <t>0,0; 28,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,74</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,13</t>
+          <t>0,0; 14,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,69</t>
+          <t>0,0; 13,78</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,63</t>
+          <t>0,0; 25,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,55</t>
+          <t>0,0; 32,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,18</t>
+          <t>0,0; 38,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,66</t>
+          <t>0,0; 21,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,73</t>
+          <t>0,0; 18,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 11,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,74</t>
+          <t>0,0; 15,58</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,33</t>
+          <t>0,0; 44,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,86</t>
+          <t>0,0; 31,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,53</t>
+          <t>0,0; 25,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,52</t>
+          <t>0,0; 24,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,37</t>
+          <t>0,0; 16,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 17,86</t>
+          <t>1,87; 18,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,26</t>
+          <t>0,0; 19,23</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,31</t>
+          <t>1,42; 13,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,09</t>
+          <t>2,18; 13,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 13,84</t>
+          <t>1,15; 11,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,72</t>
+          <t>1,1; 11,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,61</t>
+          <t>0,0; 11,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,87</t>
+          <t>1,42; 8,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,32</t>
+          <t>2,18; 8,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,93</t>
+          <t>1,65; 9,34</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de cabeza (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4348</t>
+          <t>0; 3223</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3634</t>
+          <t>0; 2809</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4255</t>
+          <t>0; 4697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>0; 3407</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>0; 4855</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5251</t>
+          <t>0; 5433</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>0; 4243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2939</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3380</t>
+          <t>0; 3387</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4410</t>
+          <t>0; 4380</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2751</t>
+          <t>0; 3389</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5039</t>
+          <t>0; 4709</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5263</t>
+          <t>0; 4936</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3127</t>
+          <t>0; 3234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2971</t>
+          <t>0; 3018</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2664</t>
+          <t>0; 3212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4250</t>
+          <t>0; 3478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4138</t>
+          <t>0; 3889</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2691</t>
+          <t>0; 3215</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4334</t>
+          <t>0; 4289</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4022</t>
+          <t>0; 4858</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4823</t>
+          <t>0; 3716</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4964</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3532</t>
+          <t>0; 2945</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>681; 6546</t>
+          <t>685; 6858</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3133</t>
+          <t>0; 4545</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>631; 5838</t>
+          <t>625; 5714</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1321; 7408</t>
+          <t>1339; 7993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>645; 7630</t>
+          <t>632; 6543</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4515</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>699; 7449</t>
+          <t>697; 7349</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6036</t>
+          <t>0; 5371</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1283; 7126</t>
+          <t>1285; 7474</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2760; 11640</t>
+          <t>2718; 10619</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1413; 9195</t>
+          <t>1699; 9614</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$cabeza-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$cabeza-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,58%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,77%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,39</t>
+          <t>0,0; 34,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 31,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,37</t>
+          <t>0,0; 16,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 50,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,42</t>
+          <t>0,0; 15,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,75</t>
+          <t>0,0; 17,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,97</t>
+          <t>0,0; 36,17</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,16%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 21,1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 22,12</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,67</t>
+          <t>0,0; 28,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,16</t>
+          <t>0,0; 15,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,0</t>
+          <t>0,0; 12,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,14</t>
+          <t>0,0; 12,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,78</t>
+          <t>0,0; 13,05</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,98%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>6,97%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,47</t>
+          <t>0,0; 39,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 28,89</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 20,75</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 29,3</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 38,81</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 21,81</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,54</t>
+          <t>0,0; 21,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,68</t>
+          <t>0,0; 12,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,58</t>
+          <t>0,0; 16,04</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,36%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,24</t>
+          <t>0,0; 24,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 45,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,24</t>
+          <t>0,0; 26,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,98</t>
+          <t>0,0; 20,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 18,71</t>
+          <t>1,9; 16,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,23</t>
+          <t>0,0; 17,7</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,92%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,59%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,02</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,04</t>
+          <t>1,09; 10,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,87</t>
+          <t>0,0; 13,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>1,46; 12,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,56</t>
+          <t>2,17; 12,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,22</t>
+          <t>1,14; 12,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,25</t>
+          <t>1,44; 9,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,51</t>
+          <t>1,87; 9,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,34</t>
+          <t>1,54; 9,06</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1133</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3223</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2809</t>
+          <t>0; 3554</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4697</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3892</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3407</t>
+          <t>0; 2842</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4437</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>0; 3806</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4855</t>
+          <t>0; 4795</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5433</t>
+          <t>0; 5784</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1373</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>626</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 3407</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4243</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3177</t>
+          <t>0; 4425</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3387</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4777</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4380</t>
+          <t>0; 3141</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3389</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4709</t>
+          <t>0; 4301</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4936</t>
+          <t>0; 4675</t>
         </is>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3234</t>
+          <t>0; 3243</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3018</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 4606</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2635</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2758</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3212</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3478</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3889</t>
+          <t>0; 4431</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3215</t>
+          <t>0; 3390</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4289</t>
+          <t>0; 4417</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1633</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>720</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1633</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3035</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4858</t>
+          <t>0; 5158</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3716</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5116</t>
+          <t>0; 4149</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4238</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2945</t>
+          <t>0; 3604</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>685; 6858</t>
+          <t>696; 6085</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4545</t>
+          <t>0; 4182</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2158</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3517</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2531</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2472</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1809</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>625; 5714</t>
+          <t>0; 4153</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1339; 7993</t>
+          <t>690; 6601</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>632; 6543</t>
+          <t>0; 6241</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>639; 5567</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>697; 7349</t>
+          <t>1329; 7782</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5371</t>
+          <t>627; 6756</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1285; 7474</t>
+          <t>1304; 8444</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2718; 10619</t>
+          <t>2335; 11319</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1699; 9614</t>
+          <t>1581; 9329</t>
         </is>
       </c>
     </row>
